--- a/questionnaire_templates/007_database_concepts_checklist--questionnaire_templates.xlsx
+++ b/questionnaire_templates/007_database_concepts_checklist--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>database_index</t>
+          <t>index_types</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Database Index</t>
+          <t>Index Types</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>index_types</t>
+          <t>query_language</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Index Types</t>
+          <t>Query Language</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>query_language</t>
+          <t>database_design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Query Language</t>
+          <t>Database Design</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>database_modeling</t>
+          <t>database_terminology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Database Modeling</t>
+          <t>Database Terminology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>data_modeling</t>
+          <t>database_schema</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Data Modeling</t>
+          <t>Database Schema</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>database_design</t>
+          <t>data_architecture</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Database Design</t>
+          <t>Data Architecture</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>database_terminology</t>
+          <t>database_modeling</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Database Terminology</t>
+          <t>Database Modeling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>database_schema</t>
+          <t>database_administration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Database Schema</t>
+          <t>Database Administration</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>data_architecture</t>
+          <t>query_language_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Data Architecture</t>
+          <t>Query Language 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>query_language</t>
+          <t>data_models</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Query Language</t>
+          <t>Data Models</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data_models</t>
+          <t>database_design_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Data Models</t>
+          <t>Database Design 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data_modeling</t>
+          <t>database_terminology_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data Modeling</t>
+          <t>Database Terminology 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>database_administration</t>
+          <t>database_administration_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Database Administration</t>
+          <t>Database Administration 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>database_security</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Database Security</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>database_index</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Database Index</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>index_types</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Index Types</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>data_architecture</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Data Architecture</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>database_modeling</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Database Modeling</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>database_administration</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Database Administration</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1466,34 +1328,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>database_modeling_choices</t>
+          <t>database_design_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>relational</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Relational</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>database_modeling_choices</t>
+          <t>database_design_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>object-oriented</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Object-Oriented</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1367,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>relational</t>
+          <t>nosql</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Relational</t>
+          <t>NoSQL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>database_design_choices</t>
+          <t>database_terminology_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>object-oriented</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Object-Oriented</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>database_design_choices</t>
+          <t>database_terminology_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nosql</t>
+          <t>foreign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NoSQL</t>
+          <t>Foreign</t>
         </is>
       </c>
     </row>
@@ -1556,46 +1418,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>clustered</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Clustered</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>database_terminology_choices</t>
+          <t>database_schema_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>foreign</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foreign</t>
+          <t>Schema</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>database_terminology_choices</t>
+          <t>database_schema_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>clustered</t>
+          <t>catalog</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clustered</t>
+          <t>Catalog</t>
         </is>
       </c>
     </row>
@@ -1607,335 +1469,114 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>namespace</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schema</t>
+          <t>Namespace</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>database_schema_choices</t>
+          <t>query_language_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Catalog</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>database_schema_choices</t>
+          <t>query_language_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>namespace</t>
+          <t>query</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Namespace</t>
+          <t>Query</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>data_architecture_choices</t>
+          <t>query_language_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>data_architecture_choices</t>
+          <t>data_models_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>entity-attribute</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Entity-Attribute</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>query_language_choices</t>
+          <t>data_models_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>class-attribute</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Class-Attribute</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>query_language_choices</t>
+          <t>data_models_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>query</t>
+          <t>document-model</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Query</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>query_language_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>java</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>data_models_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>entity-attribute</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Entity-Attribute</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>data_models_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>class-attribute</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Class-Attribute</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>data_models_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>document-model</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
           <t>Document-Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>database_administration_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>backup</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>database_administration_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>database_administration_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>maintenance</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>database_security_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>authentication</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>database_security_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>authorization</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>database_security_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>encryption</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Encryption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>index_types_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>b-tree_index</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>B-Tree Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>index_types_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>hash_index</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Hash Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>index_types_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>full_text_search</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Full Text Search</t>
         </is>
       </c>
     </row>
